--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.98532688917064</v>
+        <v>9.422615619490228</v>
       </c>
       <c r="D2" t="n">
-        <v>7.106335201775948</v>
+        <v>1.154779470288592</v>
       </c>
       <c r="E2" t="n">
-        <v>14.47308397892632</v>
+        <v>2.351876146575528</v>
       </c>
       <c r="F2" t="n">
-        <v>17.56009869242204</v>
+        <v>2.853516037518581</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.50118357713117</v>
+        <v>6.418942331283815</v>
       </c>
       <c r="D3" t="n">
-        <v>32.38054971738435</v>
+        <v>5.261839329074958</v>
       </c>
       <c r="E3" t="n">
-        <v>14.47308397892632</v>
+        <v>2.351876146575528</v>
       </c>
       <c r="F3" t="n">
-        <v>17.56009869242204</v>
+        <v>2.853516037518581</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.71728409722168</v>
+        <v>6.291558665798523</v>
       </c>
       <c r="D4" t="n">
-        <v>12.97026554391903</v>
+        <v>2.107668150886842</v>
       </c>
       <c r="E4" t="n">
-        <v>14.47308397892632</v>
+        <v>2.351876146575528</v>
       </c>
       <c r="F4" t="n">
-        <v>17.56009869242204</v>
+        <v>2.853516037518581</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.17951803627394</v>
+        <v>4.091671680894515</v>
       </c>
       <c r="D5" t="n">
-        <v>24.55838010273653</v>
+        <v>3.990736766694686</v>
       </c>
       <c r="E5" t="n">
-        <v>14.47308397892632</v>
+        <v>2.351876146575528</v>
       </c>
       <c r="F5" t="n">
-        <v>17.56009869242204</v>
+        <v>2.853516037518581</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.20310958423071</v>
+        <v>4.25800530743749</v>
       </c>
       <c r="D6" t="n">
-        <v>25.77304793771975</v>
+        <v>4.188120289879459</v>
       </c>
       <c r="E6" t="n">
-        <v>14.47308397892632</v>
+        <v>2.351876146575528</v>
       </c>
       <c r="F6" t="n">
-        <v>17.56009869242204</v>
+        <v>2.853516037518581</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>49.99420332906353</v>
+        <v>8.124058040972825</v>
       </c>
       <c r="D7" t="n">
-        <v>50.77400909914441</v>
+        <v>8.250776478610968</v>
       </c>
       <c r="E7" t="n">
-        <v>14.47308397892632</v>
+        <v>2.351876146575528</v>
       </c>
       <c r="F7" t="n">
-        <v>17.56009869242204</v>
+        <v>2.853516037518581</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.90327980489921</v>
+        <v>6.646782968296122</v>
       </c>
       <c r="D8" t="n">
-        <v>42.59128995159116</v>
+        <v>6.921084617133564</v>
       </c>
       <c r="E8" t="n">
-        <v>14.47308397892632</v>
+        <v>2.351876146575528</v>
       </c>
       <c r="F8" t="n">
-        <v>17.56009869242204</v>
+        <v>2.853516037518581</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.6896782997999</v>
+        <v>6.449572723717484</v>
       </c>
       <c r="D9" t="n">
-        <v>37.70187926331361</v>
+        <v>6.126555380288463</v>
       </c>
       <c r="E9" t="n">
-        <v>14.47308397892632</v>
+        <v>2.351876146575528</v>
       </c>
       <c r="F9" t="n">
-        <v>17.56009869242204</v>
+        <v>2.853516037518581</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.72327681599815</v>
+        <v>6.455032482599699</v>
       </c>
       <c r="D10" t="n">
-        <v>37.37334595754629</v>
+        <v>6.073168718101273</v>
       </c>
       <c r="E10" t="n">
-        <v>14.47308397892632</v>
+        <v>2.351876146575528</v>
       </c>
       <c r="F10" t="n">
-        <v>17.56009869242204</v>
+        <v>2.853516037518581</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>44.5359419384691</v>
+        <v>7.237090565001229</v>
       </c>
       <c r="D11" t="n">
-        <v>46.54848692648122</v>
+        <v>7.564129125553199</v>
       </c>
       <c r="E11" t="n">
-        <v>14.47308397892632</v>
+        <v>2.351876146575528</v>
       </c>
       <c r="F11" t="n">
-        <v>17.56009869242204</v>
+        <v>2.853516037518581</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>54.08107961509223</v>
+        <v>8.788175437452487</v>
       </c>
       <c r="D12" t="n">
-        <v>56.2088420934632</v>
+        <v>9.13393684018777</v>
       </c>
       <c r="E12" t="n">
-        <v>14.47308397892632</v>
+        <v>2.351876146575528</v>
       </c>
       <c r="F12" t="n">
-        <v>17.56009869242204</v>
+        <v>2.853516037518581</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>20.48550657871322</v>
+        <v>3.328894819040898</v>
       </c>
       <c r="D13" t="n">
-        <v>14.17414215100736</v>
+        <v>2.303298099538697</v>
       </c>
       <c r="E13" t="n">
-        <v>14.47308397892632</v>
+        <v>2.351876146575528</v>
       </c>
       <c r="F13" t="n">
-        <v>17.56009869242204</v>
+        <v>2.853516037518581</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>55.88311466347507</v>
+        <v>9.081006132814698</v>
       </c>
       <c r="D14" t="n">
-        <v>57.93647013777256</v>
+        <v>9.414676397388041</v>
       </c>
       <c r="E14" t="n">
-        <v>14.47308397892632</v>
+        <v>2.351876146575528</v>
       </c>
       <c r="F14" t="n">
-        <v>17.56009869242204</v>
+        <v>2.853516037518581</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>55.75928076479171</v>
+        <v>9.060883124278654</v>
       </c>
       <c r="D15" t="n">
-        <v>57.32388994128701</v>
+        <v>9.315132115459139</v>
       </c>
       <c r="E15" t="n">
-        <v>14.47308397892632</v>
+        <v>2.351876146575528</v>
       </c>
       <c r="F15" t="n">
-        <v>17.56009869242204</v>
+        <v>2.853516037518581</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>43.26644756716318</v>
+        <v>7.030797729664018</v>
       </c>
       <c r="D16" t="n">
-        <v>40.97028344463529</v>
+        <v>6.657671059753235</v>
       </c>
       <c r="E16" t="n">
-        <v>14.47308397892632</v>
+        <v>2.351876146575528</v>
       </c>
       <c r="F16" t="n">
-        <v>17.56009869242204</v>
+        <v>2.853516037518581</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>2.499705108573387</v>
+        <v>0.4062020801431754</v>
       </c>
       <c r="D17" t="n">
-        <v>2.069499290887157</v>
+        <v>0.336293634769163</v>
       </c>
       <c r="E17" t="n">
-        <v>14.47308397892632</v>
+        <v>2.351876146575528</v>
       </c>
       <c r="F17" t="n">
-        <v>17.56009869242204</v>
+        <v>2.853516037518581</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
